--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D62097-F363-4B3C-9761-E7D488503F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747CBD8A-C069-42D4-A98C-4A3BB54D990F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="47" activeTab="48" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="40" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لودلين سادة أول" sheetId="9" r:id="rId1"/>
@@ -55,15 +55,16 @@
     <sheet name="دوا غسيل بودرا - اندومي 100 كغ" sheetId="55" r:id="rId40"/>
     <sheet name="دوا غسيل بودرا 45كغ مصنع" sheetId="52" r:id="rId41"/>
     <sheet name="طبخة دوا غسيل بودرا" sheetId="3" r:id="rId42"/>
-    <sheet name="طبخة الشامبو" sheetId="1" r:id="rId43"/>
-    <sheet name="صابون سائل ماء الذهب" sheetId="44" r:id="rId44"/>
-    <sheet name="صابون سائل عود" sheetId="45" r:id="rId45"/>
-    <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId46"/>
-    <sheet name="صابون سادة" sheetId="2" r:id="rId47"/>
-    <sheet name="طبخة ابو رفيق مغاسل 1.5 طون" sheetId="53" r:id="rId48"/>
-    <sheet name=" سائل غسيل ابو رفيق - 250كغ  " sheetId="59" r:id="rId49"/>
-    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId50"/>
-    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId51"/>
+    <sheet name="طبخة الشامبو 120 كغ" sheetId="60" r:id="rId43"/>
+    <sheet name="طبخة الشامبو" sheetId="1" r:id="rId44"/>
+    <sheet name="صابون سائل ماء الذهب" sheetId="44" r:id="rId45"/>
+    <sheet name="صابون سائل عود" sheetId="45" r:id="rId46"/>
+    <sheet name="صابون سائل رمان - لافندر" sheetId="51" r:id="rId47"/>
+    <sheet name="صابون سادة" sheetId="2" r:id="rId48"/>
+    <sheet name="طبخة ابو رفيق مغاسل 1.5 طون" sheetId="53" r:id="rId49"/>
+    <sheet name=" سائل غسيل ابو رفيق - 250كغ  " sheetId="59" r:id="rId50"/>
+    <sheet name="جدول فارغ غير قابل للتعديل" sheetId="10" r:id="rId51"/>
+    <sheet name="طبخة جديدة 2 (3)" sheetId="14" r:id="rId52"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -81,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="107">
   <si>
     <t>رقم</t>
   </si>
@@ -390,6 +391,18 @@
   </si>
   <si>
     <t>تم وضع 11 كغ + زاد 50 كغ تحتاج الى تعديل</t>
+  </si>
+  <si>
+    <t>عطر هيد اند شولدرز</t>
+  </si>
+  <si>
+    <t>ايثانول</t>
+  </si>
+  <si>
+    <t>مينتول</t>
+  </si>
+  <si>
+    <t>سيتول</t>
   </si>
 </sst>
 </file>
@@ -10255,6 +10268,354 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0F2F89A-953A-44E7-ABA1-2704D4B9C075}">
+  <sheetPr>
+    <tabColor theme="1" tint="0.499984740745262"/>
+  </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="20.25" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="60.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="17">
+        <v>15</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="17">
+        <v>2</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="17">
+        <v>2</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="17">
+        <v>2</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="17">
+        <v>1</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="17">
+        <v>200</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="17">
+        <v>500</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="17">
+        <v>1</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A10" s="17">
+        <v>10</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="17">
+        <v>200</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A11" s="17">
+        <v>11</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="17">
+        <v>500</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A12" s="17">
+        <v>12</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="17">
+        <v>95</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+    </row>
+    <row r="14" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+    </row>
+    <row r="15" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+    </row>
+    <row r="16" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+    </row>
+    <row r="17" spans="1:5" s="19" customFormat="1" ht="27">
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+    </row>
+    <row r="18" spans="1:5" s="19" customFormat="1" ht="27.75">
+      <c r="A18" s="21"/>
+      <c r="B18" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="38"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="1:5" ht="16.5">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="1:5" ht="16.5">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="1:5" ht="16.5">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+    </row>
+    <row r="26" spans="1:5" ht="16.5">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+    </row>
+    <row r="27" spans="1:5" ht="16.5">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+    </row>
+    <row r="28" spans="1:5" ht="16.5">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+    </row>
+    <row r="29" spans="1:5" ht="16.5">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+    </row>
+    <row r="30" spans="1:5" ht="16.5">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+    </row>
+    <row r="31" spans="1:5" ht="16.5">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+    </row>
+    <row r="32" spans="1:5" ht="16.5">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B18:E18"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.34" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet25">
     <tabColor theme="1" tint="0.499984740745262"/>
@@ -10617,7 +10978,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD54551-29D1-C248-BCC3-669AAD78D534}">
   <sheetPr codeName="Sheet33">
     <tabColor rgb="FFD3C800"/>
@@ -10948,7 +11309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5622BACE-1212-6445-8A30-E1A04DAA8C98}">
   <sheetPr codeName="Sheet38">
     <tabColor theme="2" tint="-0.749992370372631"/>
@@ -11279,7 +11640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FECB2919-8233-4E01-B177-AF5E1DA3FCB4}">
   <sheetPr>
     <tabColor theme="3" tint="0.39997558519241921"/>
@@ -11610,7 +11971,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet26">
     <tabColor theme="0" tint="-0.249977111117893"/>
@@ -11915,7 +12276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D918CC59-206B-4E6F-B4B9-D188C671F6A6}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
@@ -12155,275 +12516,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.65" top="2.44" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="256" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F8F46B4-9058-44FB-9595-2DA7A55AB709}">
-  <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="18">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1.3</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="4">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="4">
-        <v>15</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="4"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="4">
-        <v>200</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="4"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="4">
-        <v>2</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="4"/>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" ht="16.5">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" ht="16.5">
-      <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B22:E22"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12682,6 +12774,275 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F8F46B4-9058-44FB-9595-2DA7A55AB709}">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="4">
+        <v>1.3</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:5" ht="16.5">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="4"/>
+    </row>
+    <row r="4" spans="1:5" ht="16.5">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="4">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="4"/>
+    </row>
+    <row r="5" spans="1:5" ht="16.5">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="4">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:5" ht="16.5">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16.5">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="4">
+        <v>200</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4"/>
+    </row>
+    <row r="9" spans="1:5" ht="16.5">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="4">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="4"/>
+    </row>
+    <row r="10" spans="1:5" ht="16.5">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="4">
+        <v>2</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4"/>
+    </row>
+    <row r="11" spans="1:5" ht="16.5">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" ht="16.5">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="16.5">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="16.5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="16.5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="16.5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="16.5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="16.5">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="16.5">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="16.5">
+      <c r="A22" s="5"/>
+      <c r="B22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B22:E22"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Sheet32"/>
   <dimension ref="A1:E22"/>
@@ -12869,7 +13230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79EE76D-5733-3243-8B4C-150C94FDB466}">
   <sheetPr codeName="Sheet34"/>
   <dimension ref="A1:E22"/>

--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747CBD8A-C069-42D4-A98C-4A3BB54D990F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62252C06-CCB1-4302-AB68-1C42291DF76A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="40" activeTab="42" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="108">
   <si>
     <t>رقم</t>
   </si>
@@ -396,13 +396,16 @@
     <t>عطر هيد اند شولدرز</t>
   </si>
   <si>
-    <t>ايثانول</t>
-  </si>
-  <si>
     <t>مينتول</t>
   </si>
   <si>
     <t>سيتول</t>
+  </si>
+  <si>
+    <t>تري ايثانول كحولي امين سعودي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تم تعطيل هذه المادة بعد تجربتها , وحذفها من الطبخة </t>
   </si>
 </sst>
 </file>
@@ -10359,12 +10362,12 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:5" s="19" customFormat="1" ht="27">
+    <row r="6" spans="1:5" s="19" customFormat="1" ht="54">
       <c r="A6" s="17">
         <v>5</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C6" s="17">
         <v>1</v>
@@ -10372,7 +10375,9 @@
       <c r="D6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="18" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="7" spans="1:5" s="19" customFormat="1" ht="27">
       <c r="A7" s="17">
@@ -10394,7 +10399,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8" s="17">
         <v>500</v>
@@ -10409,7 +10414,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="17">
         <v>1</v>

--- a/مرجع-الطبخات.xlsx
+++ b/مرجع-الطبخات.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\ملفات خاصة بالمعمل ووظائفه\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0550C71-5C82-430A-B55A-C51C6FE1ECA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{170A14F9-177B-4688-81A6-90D6760A476A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="41" activeTab="44" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="656" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="لودلين سادة اندومي" sheetId="61" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="114">
   <si>
     <t>رقم</t>
   </si>
@@ -424,6 +424,9 @@
   <si>
     <t xml:space="preserve">طبخة شامبو أبو رفيق طون تم تقسيمها ال 300 </t>
   </si>
+  <si>
+    <t xml:space="preserve"> عطرلافندر من تبعات أيوب</t>
+  </si>
 </sst>
 </file>
 
@@ -629,7 +632,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -686,6 +689,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -710,11 +718,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="عادي" xfId="0" builtinId="0"/>
@@ -1146,12 +1152,12 @@
     </row>
     <row r="9" spans="1:5" ht="28.5" customHeight="1">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -1423,12 +1429,12 @@
     </row>
     <row r="13" spans="1:5" ht="24" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -1693,12 +1699,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -1951,12 +1957,12 @@
     </row>
     <row r="12" spans="1:6" ht="21" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:6" ht="16.5">
       <c r="A13" s="4"/>
@@ -2225,12 +2231,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -2494,12 +2500,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -2764,12 +2770,12 @@
     </row>
     <row r="13" spans="1:5" ht="18.75" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -3013,12 +3019,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -3029,12 +3035,12 @@
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="5"/>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
     </row>
     <row r="15" spans="1:5" ht="16.5">
       <c r="A15" s="4"/>
@@ -3256,12 +3262,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -3532,12 +3538,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="14"/>
@@ -3802,12 +3808,12 @@
     </row>
     <row r="13" spans="1:5" ht="21" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -4039,12 +4045,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -4316,12 +4322,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="35"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="38"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -4576,12 +4582,12 @@
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -4850,12 +4856,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -5119,12 +5125,12 @@
     </row>
     <row r="13" spans="1:5" ht="23.25" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="4"/>
@@ -5389,12 +5395,12 @@
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -5665,12 +5671,12 @@
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
       <c r="A13" s="9"/>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="29"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="10"/>
@@ -5841,12 +5847,12 @@
     </row>
     <row r="8" spans="1:5" ht="27.75" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -6062,12 +6068,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -6283,12 +6289,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="9"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="13"/>
@@ -6515,12 +6521,12 @@
     </row>
     <row r="8" spans="1:5" ht="32.25" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -6787,12 +6793,12 @@
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1">
       <c r="A12" s="9"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="10"/>
@@ -6935,12 +6941,12 @@
     </row>
     <row r="8" spans="1:5" ht="30" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -7170,12 +7176,12 @@
     </row>
     <row r="8" spans="1:5" ht="31.5" customHeight="1">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -7391,12 +7397,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="8"/>
@@ -7617,12 +7623,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7837,12 +7843,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -8014,12 +8020,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -8318,12 +8324,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -8622,12 +8628,12 @@
     </row>
     <row r="11" spans="1:5" ht="16.5">
       <c r="A11" s="5"/>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="4"/>
@@ -8981,12 +8987,12 @@
     </row>
     <row r="25" spans="1:5" ht="16.5">
       <c r="A25" s="5"/>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="26"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9116,12 +9122,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -9427,12 +9433,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="14"/>
@@ -9626,12 +9632,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -9867,12 +9873,12 @@
     </row>
     <row r="8" spans="1:5" ht="16.5">
       <c r="A8" s="5"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="4"/>
@@ -10121,12 +10127,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -10376,12 +10382,12 @@
     </row>
     <row r="9" spans="1:5" ht="16.5">
       <c r="A9" s="5"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="4"/>
@@ -10721,12 +10727,12 @@
     </row>
     <row r="14" spans="1:5" s="19" customFormat="1" ht="32.25" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="36" t="s">
+      <c r="B14" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5" ht="16.5">
       <c r="A15" s="10"/>
@@ -10967,12 +10973,12 @@
     </row>
     <row r="9" spans="1:5" s="19" customFormat="1" ht="27.75">
       <c r="A9" s="21"/>
-      <c r="B9" s="36" t="s">
+      <c r="B9" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
     </row>
     <row r="10" spans="1:5" ht="16.5">
       <c r="A10" s="10"/>
@@ -11330,12 +11336,12 @@
     </row>
     <row r="19" spans="1:5" s="19" customFormat="1" ht="27.75">
       <c r="A19" s="21"/>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="38"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:5" ht="16.5">
       <c r="A20" s="10"/>
@@ -11760,12 +11766,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12091,12 +12097,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12422,12 +12428,12 @@
     </row>
     <row r="32" spans="1:5" ht="16.5">
       <c r="A32" s="5"/>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="26"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -12611,12 +12617,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="4"/>
@@ -13222,12 +13228,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13491,12 +13497,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13679,12 +13685,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13867,12 +13873,12 @@
     </row>
     <row r="22" spans="1:5" ht="16.5">
       <c r="A22" s="5"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14057,12 +14063,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="9"/>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="10"/>
@@ -14313,12 +14319,12 @@
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="35"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -14329,12 +14335,12 @@
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="5"/>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29"/>
     </row>
     <row r="15" spans="1:5" ht="16.5">
       <c r="A15" s="4"/>
@@ -14380,7 +14386,7 @@
     <tabColor rgb="FF7030A0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -14407,164 +14413,164 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" s="7">
+    <row r="2" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="8">
         <v>150</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" ht="16.5">
-      <c r="A3" s="7">
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="8"/>
+    </row>
+    <row r="3" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="8">
         <v>100</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="7"/>
-    </row>
-    <row r="4" spans="1:5" ht="16.5">
-      <c r="A4" s="7">
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <v>19</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" spans="1:5" ht="16.5">
-      <c r="A5" s="7">
+      <c r="D4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <v>5</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5">
-      <c r="A6" s="7">
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <v>1.5</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" spans="1:5" ht="16.5">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <v>50</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:5" ht="16.5">
-      <c r="A8" s="7">
+      <c r="D7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" spans="1:5" ht="16.5">
-      <c r="A9" s="7">
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>675</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" spans="1:5" ht="16.5">
-      <c r="A10" s="7">
+      <c r="D9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>2</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16.5">
-      <c r="A11" s="7">
+      <c r="D10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="39" customFormat="1" ht="23.25" customHeight="1">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <v>25</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.5">
       <c r="A12" s="5"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:5" ht="16.5">
       <c r="A13" s="4"/>
@@ -14572,62 +14578,6 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="16.5">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="16.5">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="16.5">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="16.5">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="16.5">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="16.5">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="16.5">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -14836,12 +14786,12 @@
     </row>
     <row r="13" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="5"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:5" ht="16.5">
       <c r="A14" s="14"/>
